--- a/Matlab/Output/Source_data/normalization_ReCiPe_individual.xlsx
+++ b/Matlab/Output/Source_data/normalization_ReCiPe_individual.xlsx
@@ -8,29 +8,28 @@
   <sheets>
     <sheet name="acidification- terrestrial" sheetId="1" r:id="rId2"/>
     <sheet name="climate change" sheetId="2" r:id="rId4"/>
-    <sheet name="climate change w bio" sheetId="3" r:id="rId5"/>
-    <sheet name="ecotoxicity- freshwater" sheetId="4" r:id="rId6"/>
-    <sheet name="ecotoxicity- marine" sheetId="5" r:id="rId7"/>
-    <sheet name="ecotoxicity- terrestrial" sheetId="6" r:id="rId8"/>
-    <sheet name="energy resources depletion- non" sheetId="7" r:id="rId9"/>
-    <sheet name="eutrophication- freshwater" sheetId="8" r:id="rId10"/>
-    <sheet name="eutrophication- marine" sheetId="9" r:id="rId11"/>
-    <sheet name="human toxicity- carcinogenic" sheetId="10" r:id="rId12"/>
-    <sheet name="human toxicity- non-carcinogeni" sheetId="11" r:id="rId13"/>
-    <sheet name="ionising radiation" sheetId="12" r:id="rId14"/>
-    <sheet name="land use" sheetId="13" r:id="rId15"/>
-    <sheet name="material resources- metals-mine" sheetId="14" r:id="rId16"/>
-    <sheet name="ozone depletion" sheetId="15" r:id="rId17"/>
-    <sheet name="particulate matter formation" sheetId="16" r:id="rId18"/>
-    <sheet name="photochemical oxidant formation" sheetId="17" r:id="rId19"/>
-    <sheet name="water use" sheetId="18" r:id="rId20"/>
+    <sheet name="ecotoxicity- freshwater" sheetId="3" r:id="rId5"/>
+    <sheet name="ecotoxicity- marine" sheetId="4" r:id="rId6"/>
+    <sheet name="ecotoxicity- terrestrial" sheetId="5" r:id="rId7"/>
+    <sheet name="energy resources depletion- non" sheetId="6" r:id="rId8"/>
+    <sheet name="eutrophication- freshwater" sheetId="7" r:id="rId9"/>
+    <sheet name="eutrophication- marine" sheetId="8" r:id="rId10"/>
+    <sheet name="human toxicity- carcinogenic" sheetId="9" r:id="rId11"/>
+    <sheet name="human toxicity- non-carcinogeni" sheetId="10" r:id="rId12"/>
+    <sheet name="ionising radiation" sheetId="11" r:id="rId13"/>
+    <sheet name="land use" sheetId="12" r:id="rId14"/>
+    <sheet name="material resources- metals-mine" sheetId="13" r:id="rId15"/>
+    <sheet name="ozone depletion" sheetId="14" r:id="rId16"/>
+    <sheet name="particulate matter formation" sheetId="15" r:id="rId17"/>
+    <sheet name="photochemical oxidant formation" sheetId="16" r:id="rId18"/>
+    <sheet name="water use" sheetId="17" r:id="rId19"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="90" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -535,447 +534,6 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="11.453125" customWidth="true"/>
-    <col min="3" max="3" width="11.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
-    <col min="5" max="5" width="11.453125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2">
-        <v>21.629227445472694</v>
-      </c>
-      <c r="C2">
-        <v>2.9466000815769009</v>
-      </c>
-      <c r="D2">
-        <v>2.1305778641082171</v>
-      </c>
-      <c r="E2">
-        <v>26.706405391157812</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2001</v>
-      </c>
-      <c r="B3">
-        <v>20.531530753269283</v>
-      </c>
-      <c r="C3">
-        <v>2.9891631643871723</v>
-      </c>
-      <c r="D3">
-        <v>2.1670721822731407</v>
-      </c>
-      <c r="E3">
-        <v>25.687766099929597</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2002</v>
-      </c>
-      <c r="B4">
-        <v>20.019921885600755</v>
-      </c>
-      <c r="C4">
-        <v>3.0390811014580423</v>
-      </c>
-      <c r="D4">
-        <v>2.2112763324666949</v>
-      </c>
-      <c r="E4">
-        <v>25.270279319525493</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2003</v>
-      </c>
-      <c r="B5">
-        <v>20.405632472542351</v>
-      </c>
-      <c r="C5">
-        <v>3.0999907051806943</v>
-      </c>
-      <c r="D5">
-        <v>2.2651912001102645</v>
-      </c>
-      <c r="E5">
-        <v>25.770814377833311</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2004</v>
-      </c>
-      <c r="B6">
-        <v>26.506706604439369</v>
-      </c>
-      <c r="C6">
-        <v>3.1769479412343387</v>
-      </c>
-      <c r="D6">
-        <v>2.3349864520372892</v>
-      </c>
-      <c r="E6">
-        <v>32.018640997710996</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2005</v>
-      </c>
-      <c r="B7">
-        <v>25.306616840405759</v>
-      </c>
-      <c r="C7">
-        <v>3.2589840493182951</v>
-      </c>
-      <c r="D7">
-        <v>2.4131194094638913</v>
-      </c>
-      <c r="E7">
-        <v>30.978720299187945</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>2006</v>
-      </c>
-      <c r="B8">
-        <v>25.115909172224072</v>
-      </c>
-      <c r="C8">
-        <v>3.3456958185416648</v>
-      </c>
-      <c r="D8">
-        <v>2.4989741198360282</v>
-      </c>
-      <c r="E8">
-        <v>30.960579110601763</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>2007</v>
-      </c>
-      <c r="B9">
-        <v>30.12030935439714</v>
-      </c>
-      <c r="C9">
-        <v>3.4362168772426767</v>
-      </c>
-      <c r="D9">
-        <v>2.6008928793731214</v>
-      </c>
-      <c r="E9">
-        <v>36.157419111012935</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2008</v>
-      </c>
-      <c r="B10">
-        <v>25.561693323766924</v>
-      </c>
-      <c r="C10">
-        <v>3.487598943703754</v>
-      </c>
-      <c r="D10">
-        <v>2.6660435919685135</v>
-      </c>
-      <c r="E10">
-        <v>31.715335859439193</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>2009</v>
-      </c>
-      <c r="B11">
-        <v>22.890672937182956</v>
-      </c>
-      <c r="C11">
-        <v>3.5413734199724156</v>
-      </c>
-      <c r="D11">
-        <v>2.7325015581021272</v>
-      </c>
-      <c r="E11">
-        <v>29.164547915257501</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>2010</v>
-      </c>
-      <c r="B12">
-        <v>29.697973444562781</v>
-      </c>
-      <c r="C12">
-        <v>3.6218096003126106</v>
-      </c>
-      <c r="D12">
-        <v>2.8166055043428329</v>
-      </c>
-      <c r="E12">
-        <v>36.136388549218225</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>2011</v>
-      </c>
-      <c r="B13">
-        <v>32.181978096749212</v>
-      </c>
-      <c r="C13">
-        <v>3.6907523482729681</v>
-      </c>
-      <c r="D13">
-        <v>2.9017241418893009</v>
-      </c>
-      <c r="E13">
-        <v>38.774454586911482</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>2012</v>
-      </c>
-      <c r="B14">
-        <v>32.270312317000055</v>
-      </c>
-      <c r="C14">
-        <v>3.7569923158282785</v>
-      </c>
-      <c r="D14">
-        <v>2.982875571852615</v>
-      </c>
-      <c r="E14">
-        <v>39.01018020468095</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>2013</v>
-      </c>
-      <c r="B15">
-        <v>33.324604895503249</v>
-      </c>
-      <c r="C15">
-        <v>3.8048682184975382</v>
-      </c>
-      <c r="D15">
-        <v>3.0509096080367564</v>
-      </c>
-      <c r="E15">
-        <v>40.180382722037542</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2014</v>
-      </c>
-      <c r="B16">
-        <v>33.629446216412632</v>
-      </c>
-      <c r="C16">
-        <v>3.8442146470169667</v>
-      </c>
-      <c r="D16">
-        <v>3.1156621196519465</v>
-      </c>
-      <c r="E16">
-        <v>40.589322983081544</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2015</v>
-      </c>
-      <c r="B17">
-        <v>35.498356105272649</v>
-      </c>
-      <c r="C17">
-        <v>3.8818286415703103</v>
-      </c>
-      <c r="D17">
-        <v>3.1804356005440035</v>
-      </c>
-      <c r="E17">
-        <v>42.560620347386958</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>2016</v>
-      </c>
-      <c r="B18">
-        <v>35.765712346252542</v>
-      </c>
-      <c r="C18">
-        <v>3.9165802098041649</v>
-      </c>
-      <c r="D18">
-        <v>3.2408781032888259</v>
-      </c>
-      <c r="E18">
-        <v>42.923170659345537</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>2017</v>
-      </c>
-      <c r="B19">
-        <v>37.532123014477399</v>
-      </c>
-      <c r="C19">
-        <v>3.9508872156038426</v>
-      </c>
-      <c r="D19">
-        <v>3.3091615236876613</v>
-      </c>
-      <c r="E19">
-        <v>44.792171753768905</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>2018</v>
-      </c>
-      <c r="B20">
-        <v>35.390410602878596</v>
-      </c>
-      <c r="C20">
-        <v>3.9414837009280421</v>
-      </c>
-      <c r="D20">
-        <v>3.3470800599395005</v>
-      </c>
-      <c r="E20">
-        <v>42.678974363746136</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>2019</v>
-      </c>
-      <c r="B21">
-        <v>33.236661131876062</v>
-      </c>
-      <c r="C21">
-        <v>3.9615704811614876</v>
-      </c>
-      <c r="D21">
-        <v>3.4064692453446219</v>
-      </c>
-      <c r="E21">
-        <v>40.604700858382174</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>2020</v>
-      </c>
-      <c r="B22">
-        <v>33.314497072240719</v>
-      </c>
-      <c r="C22">
-        <v>3.9151089937202368</v>
-      </c>
-      <c r="D22">
-        <v>3.418709457414463</v>
-      </c>
-      <c r="E22">
-        <v>40.648315523375423</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>2021</v>
-      </c>
-      <c r="B23">
-        <v>42.698362997890698</v>
-      </c>
-      <c r="C23">
-        <v>4.018930613573632</v>
-      </c>
-      <c r="D23">
-        <v>3.557060207373143</v>
-      </c>
-      <c r="E23">
-        <v>50.274353818837469</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>2022</v>
-      </c>
-      <c r="B24">
-        <v>42.405916804846946</v>
-      </c>
-      <c r="C24">
-        <v>4.0004440074267631</v>
-      </c>
-      <c r="D24">
-        <v>3.6143709279862848</v>
-      </c>
-      <c r="E24">
-        <v>50.020731740259997</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>2023</v>
-      </c>
-      <c r="B25">
-        <v>30.473718717161006</v>
-      </c>
-      <c r="C25">
-        <v>3.9207802958488962</v>
-      </c>
-      <c r="D25">
-        <v>3.592205976150507</v>
-      </c>
-      <c r="E25">
-        <v>37.986704989160415</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="4.90625" customWidth="true"/>
     <col min="2" max="2" width="13.453125" customWidth="true"/>
     <col min="3" max="3" width="14.453125" customWidth="true"/>
     <col min="4" max="4" width="14.453125" customWidth="true"/>
@@ -1411,7 +969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1852,7 +1410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2293,7 +1851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2734,7 +2292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3175,7 +2733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3616,7 +3174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4057,7 +3615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4945,10 +4503,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="13.453125" customWidth="true"/>
-    <col min="3" max="3" width="13.453125" customWidth="true"/>
-    <col min="4" max="4" width="13.453125" customWidth="true"/>
-    <col min="5" max="5" width="12.453125" customWidth="true"/>
+    <col min="2" max="2" width="11.453125" customWidth="true"/>
+    <col min="3" max="3" width="12.453125" customWidth="true"/>
+    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="5" max="5" width="11.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4973,16 +4531,16 @@
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>0.025728533486185562</v>
+        <v>2.5472459039646376</v>
       </c>
       <c r="C2">
-        <v>0.0734059844548937</v>
+        <v>0.21456244263374011</v>
       </c>
       <c r="D2">
-        <v>0.013578234486857162</v>
+        <v>0.17421618561791136</v>
       </c>
       <c r="E2">
-        <v>0.11271275242793642</v>
+        <v>2.936024532216289</v>
       </c>
     </row>
     <row r="3">
@@ -4990,16 +4548,16 @@
         <v>2001</v>
       </c>
       <c r="B3">
-        <v>0.02449838157345828</v>
+        <v>2.4259100188997498</v>
       </c>
       <c r="C3">
-        <v>0.074934152164365067</v>
+        <v>0.21753519919679967</v>
       </c>
       <c r="D3">
-        <v>0.013790733624613957</v>
+        <v>0.17669709669128697</v>
       </c>
       <c r="E3">
-        <v>0.1132232673624373</v>
+        <v>2.8201423147878364</v>
       </c>
     </row>
     <row r="4">
@@ -5007,16 +4565,16 @@
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>0.02397837768636818</v>
+        <v>2.3751967171990902</v>
       </c>
       <c r="C4">
-        <v>0.076852723575124779</v>
+        <v>0.22075544355048488</v>
       </c>
       <c r="D4">
-        <v>0.014050069727739888</v>
+        <v>0.17975118405625212</v>
       </c>
       <c r="E4">
-        <v>0.11488117098923284</v>
+        <v>2.775703344805827</v>
       </c>
     </row>
     <row r="5">
@@ -5024,16 +4582,16 @@
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>0.024544582226589371</v>
+        <v>2.4323014317279141</v>
       </c>
       <c r="C5">
-        <v>0.079195371858955171</v>
+        <v>0.22463091837996424</v>
       </c>
       <c r="D5">
-        <v>0.014368432883249498</v>
+        <v>0.18352784871286659</v>
       </c>
       <c r="E5">
-        <v>0.11810838696879404</v>
+        <v>2.840460198820745</v>
       </c>
     </row>
     <row r="6">
@@ -5041,16 +4599,16 @@
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>0.03205109741326035</v>
+        <v>3.1779469898816979</v>
       </c>
       <c r="C6">
-        <v>0.082271690440004583</v>
+        <v>0.22922268768940601</v>
       </c>
       <c r="D6">
-        <v>0.014781919703618434</v>
+        <v>0.18844908612043867</v>
       </c>
       <c r="E6">
-        <v>0.12910470755688339</v>
+        <v>3.5956187636915424</v>
       </c>
     </row>
     <row r="7">
@@ -5058,16 +4616,16 @@
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>0.030786457148348732</v>
+        <v>3.0549088009394438</v>
       </c>
       <c r="C7">
-        <v>0.085887576477193209</v>
+        <v>0.2333585397941175</v>
       </c>
       <c r="D7">
-        <v>0.015247609223375877</v>
+        <v>0.19402938614252033</v>
       </c>
       <c r="E7">
-        <v>0.1319216428489178</v>
+        <v>3.4822967268760814</v>
       </c>
     </row>
     <row r="8">
@@ -5075,16 +4633,16 @@
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>0.030759019427022766</v>
+        <v>3.055876155386235</v>
       </c>
       <c r="C8">
-        <v>0.089949280592797581</v>
+        <v>0.23705925687494864</v>
       </c>
       <c r="D8">
-        <v>0.015753895916374591</v>
+        <v>0.20007768878518487</v>
       </c>
       <c r="E8">
-        <v>0.13646219593619494</v>
+        <v>3.4930131010463685</v>
       </c>
     </row>
     <row r="9">
@@ -5092,16 +4650,16 @@
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>0.037231282077271277</v>
+        <v>3.7067822422399965</v>
       </c>
       <c r="C9">
-        <v>0.095350077586048826</v>
+        <v>0.23835007113355258</v>
       </c>
       <c r="D9">
-        <v>0.016356569492050957</v>
+        <v>0.20736590748842695</v>
       </c>
       <c r="E9">
-        <v>0.14893792915537107</v>
+        <v>4.1524982208619763</v>
       </c>
     </row>
     <row r="10">
@@ -5109,16 +4667,16 @@
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>0.031814997876588452</v>
+        <v>3.173728301647547</v>
       </c>
       <c r="C10">
-        <v>0.099066352587374507</v>
+        <v>0.23817455299616441</v>
       </c>
       <c r="D10">
-        <v>0.016728899736654524</v>
+        <v>0.21178388349946159</v>
       </c>
       <c r="E10">
-        <v>0.14761025020061749</v>
+        <v>3.623686738143173</v>
       </c>
     </row>
     <row r="11">
@@ -5126,16 +4684,16 @@
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>0.028671726923452344</v>
+        <v>2.8660698960497593</v>
       </c>
       <c r="C11">
-        <v>0.10283563566461601</v>
+        <v>0.23814364440281355</v>
       </c>
       <c r="D11">
-        <v>0.017108590924986417</v>
+        <v>0.2163238486248856</v>
       </c>
       <c r="E11">
-        <v>0.14861595351305479</v>
+        <v>3.3205373890774585</v>
       </c>
     </row>
     <row r="12">
@@ -5143,16 +4701,16 @@
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>0.037448924531374168</v>
+        <v>3.7538031181991127</v>
       </c>
       <c r="C12">
-        <v>0.10786526271974416</v>
+        <v>0.23900296112692432</v>
       </c>
       <c r="D12">
-        <v>0.017591644447899037</v>
+        <v>0.22221150119144958</v>
       </c>
       <c r="E12">
-        <v>0.16290583169901737</v>
+        <v>4.215017580517487</v>
       </c>
     </row>
     <row r="13">
@@ -5160,16 +4718,16 @@
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>0.040840597791929334</v>
+        <v>4.1094342830214874</v>
       </c>
       <c r="C13">
-        <v>0.11264899106682624</v>
+        <v>0.24040456559191706</v>
       </c>
       <c r="D13">
-        <v>0.01807318259913163</v>
+        <v>0.22817845158762151</v>
       </c>
       <c r="E13">
-        <v>0.1715627714578872</v>
+        <v>4.5780173002010258</v>
       </c>
     </row>
     <row r="14">
@@ -5177,16 +4735,16 @@
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>0.041161758036921708</v>
+        <v>4.1614415711764101</v>
       </c>
       <c r="C14">
-        <v>0.11696137272304749</v>
+        <v>0.24447386804028606</v>
       </c>
       <c r="D14">
-        <v>0.018522113194426929</v>
+        <v>0.23382223830073778</v>
       </c>
       <c r="E14">
-        <v>0.17664524395439613</v>
+        <v>4.6397376775174344</v>
       </c>
     </row>
     <row r="15">
@@ -5194,16 +4752,16 @@
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>0.042723977570115229</v>
+        <v>4.3460353687221618</v>
       </c>
       <c r="C15">
-        <v>0.12039401890290137</v>
+        <v>0.25272673724841183</v>
       </c>
       <c r="D15">
-        <v>0.018878770754064994</v>
+        <v>0.23837138238323197</v>
       </c>
       <c r="E15">
-        <v>0.18199676722708161</v>
+        <v>4.8371334883538051</v>
       </c>
     </row>
     <row r="16">
@@ -5211,16 +4769,16 @@
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>0.043363497652025018</v>
+        <v>4.4446843187476857</v>
       </c>
       <c r="C16">
-        <v>0.12316537791862388</v>
+        <v>0.26774637572527593</v>
       </c>
       <c r="D16">
-        <v>0.019206097060320771</v>
+        <v>0.24261413531828038</v>
       </c>
       <c r="E16">
-        <v>0.18573497263096966</v>
+        <v>4.9550448297912419</v>
       </c>
     </row>
     <row r="17">
@@ -5228,16 +4786,16 @@
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>0.046152357566699727</v>
+        <v>4.7728981148842307</v>
       </c>
       <c r="C17">
-        <v>0.12549509953959029</v>
+        <v>0.28996134364553477</v>
       </c>
       <c r="D17">
-        <v>0.019521467305798033</v>
+        <v>0.24676297988404725</v>
       </c>
       <c r="E17">
-        <v>0.19116892441208805</v>
+        <v>5.3096224384138129</v>
       </c>
     </row>
     <row r="18">
@@ -5245,16 +4803,16 @@
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>0.046762981084376438</v>
+        <v>4.8867651593748471</v>
       </c>
       <c r="C18">
-        <v>0.1272311409703869</v>
+        <v>0.3158884149291703</v>
       </c>
       <c r="D18">
-        <v>0.019801094901889551</v>
+        <v>0.25052975434038527</v>
       </c>
       <c r="E18">
-        <v>0.19379521695665289</v>
+        <v>5.4531833286444025</v>
       </c>
     </row>
     <row r="19">
@@ -5262,16 +4820,16 @@
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>0.049434885005184157</v>
+        <v>5.2334938269783846</v>
       </c>
       <c r="C19">
-        <v>0.12815658707054922</v>
+        <v>0.35444351582274553</v>
       </c>
       <c r="D19">
-        <v>0.020109858260155638</v>
+        <v>0.25468413355428487</v>
       </c>
       <c r="E19">
-        <v>0.19770133033588902</v>
+        <v>5.842621476355415</v>
       </c>
     </row>
     <row r="20">
@@ -5279,16 +4837,16 @@
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>0.046989339162351776</v>
+        <v>5.0456652057226501</v>
       </c>
       <c r="C20">
-        <v>0.12707059070704863</v>
+        <v>0.39979049027045371</v>
       </c>
       <c r="D20">
-        <v>0.020226264260979804</v>
+        <v>0.25647844434086109</v>
       </c>
       <c r="E20">
-        <v>0.1942861941303802</v>
+        <v>5.7019341403339654</v>
       </c>
     </row>
     <row r="21">
@@ -5296,16 +4854,16 @@
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>0.044550257878242676</v>
+        <v>4.8512220839287226</v>
       </c>
       <c r="C21">
-        <v>0.1261655533942288</v>
+        <v>0.45301532581973203</v>
       </c>
       <c r="D21">
-        <v>0.020479210973007509</v>
+        <v>0.26000519215910511</v>
       </c>
       <c r="E21">
-        <v>0.19119502224547899</v>
+        <v>5.5642426019075595</v>
       </c>
     </row>
     <row r="22">
@@ -5313,16 +4871,16 @@
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>0.045315521169762715</v>
+        <v>5.0300373635679048</v>
       </c>
       <c r="C22">
-        <v>0.1229144010350174</v>
+        <v>0.51142197890264463</v>
       </c>
       <c r="D22">
-        <v>0.020419759380777246</v>
+        <v>0.25957444499931986</v>
       </c>
       <c r="E22">
-        <v>0.18864968158555737</v>
+        <v>5.8010337874698692</v>
       </c>
     </row>
     <row r="23">
@@ -5330,16 +4888,16 @@
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>0.059343827612607362</v>
+        <v>6.7288162387922181</v>
       </c>
       <c r="C23">
-        <v>0.12260626659053817</v>
+        <v>0.61628148466202426</v>
       </c>
       <c r="D23">
-        <v>0.021016134956781226</v>
+        <v>0.26676718963080626</v>
       </c>
       <c r="E23">
-        <v>0.20296622915992676</v>
+        <v>7.6118649130850482</v>
       </c>
     </row>
     <row r="24">
@@ -5347,16 +4905,16 @@
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>0.060388721553104929</v>
+        <v>7.0056737274404073</v>
       </c>
       <c r="C24">
-        <v>0.11688056413685965</v>
+        <v>0.72284512981395976</v>
       </c>
       <c r="D24">
-        <v>0.021135766408300189</v>
+        <v>0.26876493025548515</v>
       </c>
       <c r="E24">
-        <v>0.19840505209826478</v>
+        <v>7.9972837875098524</v>
       </c>
     </row>
     <row r="25">
@@ -5364,16 +4922,16 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>0.044083830285328834</v>
+        <v>5.2000409170051141</v>
       </c>
       <c r="C25">
-        <v>0.11067797737246773</v>
+        <v>0.78695757021632251</v>
       </c>
       <c r="D25">
-        <v>0.02082820099729785</v>
+        <v>0.26534222872065782</v>
       </c>
       <c r="E25">
-        <v>0.17559000865509442</v>
+        <v>6.2523407159420943</v>
       </c>
     </row>
   </sheetData>
@@ -5414,16 +4972,16 @@
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>2.5472459039646376</v>
+        <v>2.2519856403002851</v>
       </c>
       <c r="C2">
-        <v>0.21456244263374011</v>
+        <v>0.31410575971920585</v>
       </c>
       <c r="D2">
-        <v>0.17421618561791136</v>
+        <v>0.1817106466167914</v>
       </c>
       <c r="E2">
-        <v>2.936024532216289</v>
+        <v>2.7478020466362825</v>
       </c>
     </row>
     <row r="3">
@@ -5431,16 +4989,16 @@
         <v>2001</v>
       </c>
       <c r="B3">
-        <v>2.4259100188997498</v>
+        <v>2.1445221799662533</v>
       </c>
       <c r="C3">
-        <v>0.21753519919679967</v>
+        <v>0.31907797948134858</v>
       </c>
       <c r="D3">
-        <v>0.17669709669128697</v>
+        <v>0.18451578033407487</v>
       </c>
       <c r="E3">
-        <v>2.8201423147878364</v>
+        <v>2.6481159397816767</v>
       </c>
     </row>
     <row r="4">
@@ -5448,16 +5006,16 @@
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>2.3751967171990902</v>
+        <v>2.0994567144811933</v>
       </c>
       <c r="C4">
-        <v>0.22075544355048488</v>
+        <v>0.32480327405984177</v>
       </c>
       <c r="D4">
-        <v>0.17975118405625212</v>
+        <v>0.18794340681782504</v>
       </c>
       <c r="E4">
-        <v>2.775703344805827</v>
+        <v>2.6122033953588599</v>
       </c>
     </row>
     <row r="5">
@@ -5465,16 +5023,16 @@
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>2.4323014317279141</v>
+        <v>2.1496648598598327</v>
       </c>
       <c r="C5">
-        <v>0.22463091837996424</v>
+        <v>0.3317300944427104</v>
       </c>
       <c r="D5">
-        <v>0.18352784871286659</v>
+        <v>0.19215553024893026</v>
       </c>
       <c r="E5">
-        <v>2.840460198820745</v>
+        <v>2.6735504845514733</v>
       </c>
     </row>
     <row r="6">
@@ -5482,16 +5040,16 @@
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>3.1779469898816979</v>
+        <v>2.8082819443524758</v>
       </c>
       <c r="C6">
-        <v>0.22922268768940601</v>
+        <v>0.34037499624594864</v>
       </c>
       <c r="D6">
-        <v>0.18844908612043867</v>
+        <v>0.19762839047624653</v>
       </c>
       <c r="E6">
-        <v>3.5956187636915424</v>
+        <v>3.3462853310746707</v>
       </c>
     </row>
     <row r="7">
@@ -5499,16 +5057,16 @@
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>3.0549088009394438</v>
+        <v>2.699113141507949</v>
       </c>
       <c r="C7">
-        <v>0.2333585397941175</v>
+        <v>0.34931407456917579</v>
       </c>
       <c r="D7">
-        <v>0.19402938614252033</v>
+        <v>0.20379829717837006</v>
       </c>
       <c r="E7">
-        <v>3.4822967268760814</v>
+        <v>3.2522255132554951</v>
       </c>
     </row>
     <row r="8">
@@ -5516,16 +5074,16 @@
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>3.055876155386235</v>
+        <v>2.6991338680972912</v>
       </c>
       <c r="C8">
-        <v>0.23705925687494864</v>
+        <v>0.35856978710759113</v>
       </c>
       <c r="D8">
-        <v>0.20007768878518487</v>
+        <v>0.21050261510281426</v>
       </c>
       <c r="E8">
-        <v>3.4930131010463685</v>
+        <v>3.2682062703076968</v>
       </c>
     </row>
     <row r="9">
@@ -5533,16 +5091,16 @@
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>3.7067822422399965</v>
+        <v>3.2721162291274486</v>
       </c>
       <c r="C9">
-        <v>0.23835007113355258</v>
+        <v>0.3673629648493148</v>
       </c>
       <c r="D9">
-        <v>0.20736590748842695</v>
+        <v>0.21849634944463217</v>
       </c>
       <c r="E9">
-        <v>4.1524982208619763</v>
+        <v>3.8579755434213956</v>
       </c>
     </row>
     <row r="10">
@@ -5550,16 +5108,16 @@
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>3.173728301647547</v>
+        <v>2.7998957276967955</v>
       </c>
       <c r="C10">
-        <v>0.23817455299616441</v>
+        <v>0.37232002246925877</v>
       </c>
       <c r="D10">
-        <v>0.21178388349946159</v>
+        <v>0.22341994752022584</v>
       </c>
       <c r="E10">
-        <v>3.623686738143173</v>
+        <v>3.3956356976862798</v>
       </c>
     </row>
     <row r="11">
@@ -5567,16 +5125,16 @@
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>2.8660698960497593</v>
+        <v>2.5268246286593739</v>
       </c>
       <c r="C11">
-        <v>0.23814364440281355</v>
+        <v>0.37748828372770993</v>
       </c>
       <c r="D11">
-        <v>0.2163238486248856</v>
+        <v>0.2284457739635897</v>
       </c>
       <c r="E11">
-        <v>3.3205373890774585</v>
+        <v>3.1327586863506736</v>
       </c>
     </row>
     <row r="12">
@@ -5584,16 +5142,16 @@
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>3.7538031181991127</v>
+        <v>3.306394678102011</v>
       </c>
       <c r="C12">
-        <v>0.23900296112692432</v>
+        <v>0.38492043108945728</v>
       </c>
       <c r="D12">
-        <v>0.22221150119144958</v>
+        <v>0.23485853602309095</v>
       </c>
       <c r="E12">
-        <v>4.215017580517487</v>
+        <v>3.926173645214559</v>
       </c>
     </row>
     <row r="13">
@@ -5601,16 +5159,16 @@
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>4.1094342830214874</v>
+        <v>3.6154597376337319</v>
       </c>
       <c r="C13">
-        <v>0.24040456559191706</v>
+        <v>0.39253704682148582</v>
       </c>
       <c r="D13">
-        <v>0.22817845158762151</v>
+        <v>0.24132341446101538</v>
       </c>
       <c r="E13">
-        <v>4.5780173002010258</v>
+        <v>4.2493201989162328</v>
       </c>
     </row>
     <row r="14">
@@ -5618,16 +5176,16 @@
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>4.1614415711764101</v>
+        <v>3.6562813030794441</v>
       </c>
       <c r="C14">
-        <v>0.24447386804028606</v>
+        <v>0.40157678037950734</v>
       </c>
       <c r="D14">
-        <v>0.23382223830073778</v>
+        <v>0.24742538404350134</v>
       </c>
       <c r="E14">
-        <v>4.6397376775174344</v>
+        <v>4.3052834675024529</v>
       </c>
     </row>
     <row r="15">
@@ -5635,16 +5193,16 @@
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>4.3460353687221618</v>
+        <v>3.8118759835399132</v>
       </c>
       <c r="C15">
-        <v>0.25272673724841183</v>
+        <v>0.4122208732159755</v>
       </c>
       <c r="D15">
-        <v>0.23837138238323197</v>
+        <v>0.25236854962219396</v>
       </c>
       <c r="E15">
-        <v>4.8371334883538051</v>
+        <v>4.4764654063780824</v>
       </c>
     </row>
     <row r="16">
@@ -5652,16 +5210,16 @@
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>4.4446843187476857</v>
+        <v>3.890124394394074</v>
       </c>
       <c r="C16">
-        <v>0.26774637572527593</v>
+        <v>0.42693780151103089</v>
       </c>
       <c r="D16">
-        <v>0.24261413531828038</v>
+        <v>0.25698777760692737</v>
       </c>
       <c r="E16">
-        <v>4.9550448297912419</v>
+        <v>4.5740499735120324</v>
       </c>
     </row>
     <row r="17">
@@ -5669,16 +5227,16 @@
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>4.7728981148842307</v>
+        <v>4.1654445167329639</v>
       </c>
       <c r="C17">
-        <v>0.28996134364553477</v>
+        <v>0.44619370424129773</v>
       </c>
       <c r="D17">
-        <v>0.24676297988404725</v>
+        <v>0.26152310143561469</v>
       </c>
       <c r="E17">
-        <v>5.3096224384138129</v>
+        <v>4.8731613224098762</v>
       </c>
     </row>
     <row r="18">
@@ -5686,16 +5244,16 @@
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>4.8867651593748471</v>
+        <v>4.2531303852615334</v>
       </c>
       <c r="C18">
-        <v>0.3158884149291703</v>
+        <v>0.46727656259646738</v>
       </c>
       <c r="D18">
-        <v>0.25052975434038527</v>
+        <v>0.26565194784371732</v>
       </c>
       <c r="E18">
-        <v>5.4531833286444025</v>
+        <v>4.986058895701718</v>
       </c>
     </row>
     <row r="19">
@@ -5703,16 +5261,16 @@
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>5.2334938269783846</v>
+        <v>4.5392754910590742</v>
       </c>
       <c r="C19">
-        <v>0.35444351582274553</v>
+        <v>0.49683776284360159</v>
       </c>
       <c r="D19">
-        <v>0.25468413355428487</v>
+        <v>0.2702475299469464</v>
       </c>
       <c r="E19">
-        <v>5.842621476355415</v>
+        <v>5.3063607838496223</v>
       </c>
     </row>
     <row r="20">
@@ -5720,16 +5278,16 @@
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>5.0456652057226501</v>
+        <v>4.3599916757359409</v>
       </c>
       <c r="C20">
-        <v>0.39979049027045371</v>
+        <v>0.52830183564477129</v>
       </c>
       <c r="D20">
-        <v>0.25647844434086109</v>
+        <v>0.27232194491883394</v>
       </c>
       <c r="E20">
-        <v>5.7019341403339654</v>
+        <v>5.1606154562995457</v>
       </c>
     </row>
     <row r="21">
@@ -5737,16 +5295,16 @@
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>4.8512220839287226</v>
+        <v>4.1760497436168507</v>
       </c>
       <c r="C21">
-        <v>0.45301532581973203</v>
+        <v>0.5666592875937142</v>
       </c>
       <c r="D21">
-        <v>0.26000519215910511</v>
+        <v>0.27622743952847273</v>
       </c>
       <c r="E21">
-        <v>5.5642426019075595</v>
+        <v>5.0189364707390371</v>
       </c>
     </row>
     <row r="22">
@@ -5754,16 +5312,16 @@
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>5.0300373635679048</v>
+        <v>4.3069691263615679</v>
       </c>
       <c r="C22">
-        <v>0.51142197890264463</v>
+        <v>0.60424992802860744</v>
       </c>
       <c r="D22">
-        <v>0.25957444499931986</v>
+        <v>0.27601907280166332</v>
       </c>
       <c r="E22">
-        <v>5.8010337874698692</v>
+        <v>5.1872381271918382</v>
       </c>
     </row>
     <row r="23">
@@ -5771,16 +5329,16 @@
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>6.7288162387922181</v>
+        <v>5.7285265946745572</v>
       </c>
       <c r="C23">
-        <v>0.61628148466202426</v>
+        <v>0.6822695988401154</v>
       </c>
       <c r="D23">
-        <v>0.26676718963080626</v>
+        <v>0.28473948668152876</v>
       </c>
       <c r="E23">
-        <v>7.6118649130850482</v>
+        <v>6.6955356801962012</v>
       </c>
     </row>
     <row r="24">
@@ -5788,16 +5346,16 @@
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>7.0056737274404073</v>
+        <v>5.9281796533660112</v>
       </c>
       <c r="C24">
-        <v>0.72284512981395976</v>
+        <v>0.75432842584964277</v>
       </c>
       <c r="D24">
-        <v>0.26876493025548515</v>
+        <v>0.28744959279816418</v>
       </c>
       <c r="E24">
-        <v>7.9972837875098524</v>
+        <v>6.9699576720138179</v>
       </c>
     </row>
     <row r="25">
@@ -5805,16 +5363,16 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>5.2000409170051141</v>
+        <v>4.382596461892633</v>
       </c>
       <c r="C25">
-        <v>0.78695757021632251</v>
+        <v>0.79299195689279245</v>
       </c>
       <c r="D25">
-        <v>0.26534222872065782</v>
+        <v>0.28424230390361088</v>
       </c>
       <c r="E25">
-        <v>6.2523407159420943</v>
+        <v>5.4598307226890359</v>
       </c>
     </row>
   </sheetData>
@@ -5822,447 +5380,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="11.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
-    <col min="5" max="5" width="11.453125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2">
-        <v>2.2519856403002851</v>
-      </c>
-      <c r="C2">
-        <v>0.31410575971920585</v>
-      </c>
-      <c r="D2">
-        <v>0.1817106466167914</v>
-      </c>
-      <c r="E2">
-        <v>2.7478020466362825</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2001</v>
-      </c>
-      <c r="B3">
-        <v>2.1445221799662533</v>
-      </c>
-      <c r="C3">
-        <v>0.31907797948134858</v>
-      </c>
-      <c r="D3">
-        <v>0.18451578033407487</v>
-      </c>
-      <c r="E3">
-        <v>2.6481159397816767</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2002</v>
-      </c>
-      <c r="B4">
-        <v>2.0994567144811933</v>
-      </c>
-      <c r="C4">
-        <v>0.32480327405984177</v>
-      </c>
-      <c r="D4">
-        <v>0.18794340681782504</v>
-      </c>
-      <c r="E4">
-        <v>2.6122033953588599</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2003</v>
-      </c>
-      <c r="B5">
-        <v>2.1496648598598327</v>
-      </c>
-      <c r="C5">
-        <v>0.3317300944427104</v>
-      </c>
-      <c r="D5">
-        <v>0.19215553024893026</v>
-      </c>
-      <c r="E5">
-        <v>2.6735504845514733</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2004</v>
-      </c>
-      <c r="B6">
-        <v>2.8082819443524758</v>
-      </c>
-      <c r="C6">
-        <v>0.34037499624594864</v>
-      </c>
-      <c r="D6">
-        <v>0.19762839047624653</v>
-      </c>
-      <c r="E6">
-        <v>3.3462853310746707</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2005</v>
-      </c>
-      <c r="B7">
-        <v>2.699113141507949</v>
-      </c>
-      <c r="C7">
-        <v>0.34931407456917579</v>
-      </c>
-      <c r="D7">
-        <v>0.20379829717837006</v>
-      </c>
-      <c r="E7">
-        <v>3.2522255132554951</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>2006</v>
-      </c>
-      <c r="B8">
-        <v>2.6991338680972912</v>
-      </c>
-      <c r="C8">
-        <v>0.35856978710759113</v>
-      </c>
-      <c r="D8">
-        <v>0.21050261510281426</v>
-      </c>
-      <c r="E8">
-        <v>3.2682062703076968</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>2007</v>
-      </c>
-      <c r="B9">
-        <v>3.2721162291274486</v>
-      </c>
-      <c r="C9">
-        <v>0.3673629648493148</v>
-      </c>
-      <c r="D9">
-        <v>0.21849634944463217</v>
-      </c>
-      <c r="E9">
-        <v>3.8579755434213956</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2008</v>
-      </c>
-      <c r="B10">
-        <v>2.7998957276967955</v>
-      </c>
-      <c r="C10">
-        <v>0.37232002246925877</v>
-      </c>
-      <c r="D10">
-        <v>0.22341994752022584</v>
-      </c>
-      <c r="E10">
-        <v>3.3956356976862798</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>2009</v>
-      </c>
-      <c r="B11">
-        <v>2.5268246286593739</v>
-      </c>
-      <c r="C11">
-        <v>0.37748828372770993</v>
-      </c>
-      <c r="D11">
-        <v>0.2284457739635897</v>
-      </c>
-      <c r="E11">
-        <v>3.1327586863506736</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>2010</v>
-      </c>
-      <c r="B12">
-        <v>3.306394678102011</v>
-      </c>
-      <c r="C12">
-        <v>0.38492043108945728</v>
-      </c>
-      <c r="D12">
-        <v>0.23485853602309095</v>
-      </c>
-      <c r="E12">
-        <v>3.926173645214559</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>2011</v>
-      </c>
-      <c r="B13">
-        <v>3.6154597376337319</v>
-      </c>
-      <c r="C13">
-        <v>0.39253704682148582</v>
-      </c>
-      <c r="D13">
-        <v>0.24132341446101538</v>
-      </c>
-      <c r="E13">
-        <v>4.2493201989162328</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>2012</v>
-      </c>
-      <c r="B14">
-        <v>3.6562813030794441</v>
-      </c>
-      <c r="C14">
-        <v>0.40157678037950734</v>
-      </c>
-      <c r="D14">
-        <v>0.24742538404350134</v>
-      </c>
-      <c r="E14">
-        <v>4.3052834675024529</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>2013</v>
-      </c>
-      <c r="B15">
-        <v>3.8118759835399132</v>
-      </c>
-      <c r="C15">
-        <v>0.4122208732159755</v>
-      </c>
-      <c r="D15">
-        <v>0.25236854962219396</v>
-      </c>
-      <c r="E15">
-        <v>4.4764654063780824</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2014</v>
-      </c>
-      <c r="B16">
-        <v>3.890124394394074</v>
-      </c>
-      <c r="C16">
-        <v>0.42693780151103089</v>
-      </c>
-      <c r="D16">
-        <v>0.25698777760692737</v>
-      </c>
-      <c r="E16">
-        <v>4.5740499735120324</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2015</v>
-      </c>
-      <c r="B17">
-        <v>4.1654445167329639</v>
-      </c>
-      <c r="C17">
-        <v>0.44619370424129773</v>
-      </c>
-      <c r="D17">
-        <v>0.26152310143561469</v>
-      </c>
-      <c r="E17">
-        <v>4.8731613224098762</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>2016</v>
-      </c>
-      <c r="B18">
-        <v>4.2531303852615334</v>
-      </c>
-      <c r="C18">
-        <v>0.46727656259646738</v>
-      </c>
-      <c r="D18">
-        <v>0.26565194784371732</v>
-      </c>
-      <c r="E18">
-        <v>4.986058895701718</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>2017</v>
-      </c>
-      <c r="B19">
-        <v>4.5392754910590742</v>
-      </c>
-      <c r="C19">
-        <v>0.49683776284360159</v>
-      </c>
-      <c r="D19">
-        <v>0.2702475299469464</v>
-      </c>
-      <c r="E19">
-        <v>5.3063607838496223</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>2018</v>
-      </c>
-      <c r="B20">
-        <v>4.3599916757359409</v>
-      </c>
-      <c r="C20">
-        <v>0.52830183564477129</v>
-      </c>
-      <c r="D20">
-        <v>0.27232194491883394</v>
-      </c>
-      <c r="E20">
-        <v>5.1606154562995457</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>2019</v>
-      </c>
-      <c r="B21">
-        <v>4.1760497436168507</v>
-      </c>
-      <c r="C21">
-        <v>0.5666592875937142</v>
-      </c>
-      <c r="D21">
-        <v>0.27622743952847273</v>
-      </c>
-      <c r="E21">
-        <v>5.0189364707390371</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>2020</v>
-      </c>
-      <c r="B22">
-        <v>4.3069691263615679</v>
-      </c>
-      <c r="C22">
-        <v>0.60424992802860744</v>
-      </c>
-      <c r="D22">
-        <v>0.27601907280166332</v>
-      </c>
-      <c r="E22">
-        <v>5.1872381271918382</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>2021</v>
-      </c>
-      <c r="B23">
-        <v>5.7285265946745572</v>
-      </c>
-      <c r="C23">
-        <v>0.6822695988401154</v>
-      </c>
-      <c r="D23">
-        <v>0.28473948668152876</v>
-      </c>
-      <c r="E23">
-        <v>6.6955356801962012</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>2022</v>
-      </c>
-      <c r="B24">
-        <v>5.9281796533660112</v>
-      </c>
-      <c r="C24">
-        <v>0.75432842584964277</v>
-      </c>
-      <c r="D24">
-        <v>0.28744959279816418</v>
-      </c>
-      <c r="E24">
-        <v>6.9699576720138179</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>2023</v>
-      </c>
-      <c r="B25">
-        <v>4.382596461892633</v>
-      </c>
-      <c r="C25">
-        <v>0.79299195689279245</v>
-      </c>
-      <c r="D25">
-        <v>0.28424230390361088</v>
-      </c>
-      <c r="E25">
-        <v>5.4598307226890359</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6703,7 +5820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7144,7 +6261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7585,7 +6702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8024,4 +7141,445 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.90625" customWidth="true"/>
+    <col min="2" max="2" width="11.453125" customWidth="true"/>
+    <col min="3" max="3" width="11.453125" customWidth="true"/>
+    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="5" max="5" width="11.453125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2">
+        <v>21.629227445472694</v>
+      </c>
+      <c r="C2">
+        <v>2.9466000815769009</v>
+      </c>
+      <c r="D2">
+        <v>2.1305778641082171</v>
+      </c>
+      <c r="E2">
+        <v>26.706405391157812</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2001</v>
+      </c>
+      <c r="B3">
+        <v>20.531530753269283</v>
+      </c>
+      <c r="C3">
+        <v>2.9891631643871723</v>
+      </c>
+      <c r="D3">
+        <v>2.1670721822731407</v>
+      </c>
+      <c r="E3">
+        <v>25.687766099929597</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2002</v>
+      </c>
+      <c r="B4">
+        <v>20.019921885600755</v>
+      </c>
+      <c r="C4">
+        <v>3.0390811014580423</v>
+      </c>
+      <c r="D4">
+        <v>2.2112763324666949</v>
+      </c>
+      <c r="E4">
+        <v>25.270279319525493</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2003</v>
+      </c>
+      <c r="B5">
+        <v>20.405632472542351</v>
+      </c>
+      <c r="C5">
+        <v>3.0999907051806943</v>
+      </c>
+      <c r="D5">
+        <v>2.2651912001102645</v>
+      </c>
+      <c r="E5">
+        <v>25.770814377833311</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2004</v>
+      </c>
+      <c r="B6">
+        <v>26.506706604439369</v>
+      </c>
+      <c r="C6">
+        <v>3.1769479412343387</v>
+      </c>
+      <c r="D6">
+        <v>2.3349864520372892</v>
+      </c>
+      <c r="E6">
+        <v>32.018640997710996</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2005</v>
+      </c>
+      <c r="B7">
+        <v>25.306616840405759</v>
+      </c>
+      <c r="C7">
+        <v>3.2589840493182951</v>
+      </c>
+      <c r="D7">
+        <v>2.4131194094638913</v>
+      </c>
+      <c r="E7">
+        <v>30.978720299187945</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2006</v>
+      </c>
+      <c r="B8">
+        <v>25.115909172224072</v>
+      </c>
+      <c r="C8">
+        <v>3.3456958185416648</v>
+      </c>
+      <c r="D8">
+        <v>2.4989741198360282</v>
+      </c>
+      <c r="E8">
+        <v>30.960579110601763</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2007</v>
+      </c>
+      <c r="B9">
+        <v>30.12030935439714</v>
+      </c>
+      <c r="C9">
+        <v>3.4362168772426767</v>
+      </c>
+      <c r="D9">
+        <v>2.6008928793731214</v>
+      </c>
+      <c r="E9">
+        <v>36.157419111012935</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2008</v>
+      </c>
+      <c r="B10">
+        <v>25.561693323766924</v>
+      </c>
+      <c r="C10">
+        <v>3.487598943703754</v>
+      </c>
+      <c r="D10">
+        <v>2.6660435919685135</v>
+      </c>
+      <c r="E10">
+        <v>31.715335859439193</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2009</v>
+      </c>
+      <c r="B11">
+        <v>22.890672937182956</v>
+      </c>
+      <c r="C11">
+        <v>3.5413734199724156</v>
+      </c>
+      <c r="D11">
+        <v>2.7325015581021272</v>
+      </c>
+      <c r="E11">
+        <v>29.164547915257501</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2010</v>
+      </c>
+      <c r="B12">
+        <v>29.697973444562781</v>
+      </c>
+      <c r="C12">
+        <v>3.6218096003126106</v>
+      </c>
+      <c r="D12">
+        <v>2.8166055043428329</v>
+      </c>
+      <c r="E12">
+        <v>36.136388549218225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2011</v>
+      </c>
+      <c r="B13">
+        <v>32.181978096749212</v>
+      </c>
+      <c r="C13">
+        <v>3.6907523482729681</v>
+      </c>
+      <c r="D13">
+        <v>2.9017241418893009</v>
+      </c>
+      <c r="E13">
+        <v>38.774454586911482</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2012</v>
+      </c>
+      <c r="B14">
+        <v>32.270312317000055</v>
+      </c>
+      <c r="C14">
+        <v>3.7569923158282785</v>
+      </c>
+      <c r="D14">
+        <v>2.982875571852615</v>
+      </c>
+      <c r="E14">
+        <v>39.01018020468095</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2013</v>
+      </c>
+      <c r="B15">
+        <v>33.324604895503249</v>
+      </c>
+      <c r="C15">
+        <v>3.8048682184975382</v>
+      </c>
+      <c r="D15">
+        <v>3.0509096080367564</v>
+      </c>
+      <c r="E15">
+        <v>40.180382722037542</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2014</v>
+      </c>
+      <c r="B16">
+        <v>33.629446216412632</v>
+      </c>
+      <c r="C16">
+        <v>3.8442146470169667</v>
+      </c>
+      <c r="D16">
+        <v>3.1156621196519465</v>
+      </c>
+      <c r="E16">
+        <v>40.589322983081544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2015</v>
+      </c>
+      <c r="B17">
+        <v>35.498356105272649</v>
+      </c>
+      <c r="C17">
+        <v>3.8818286415703103</v>
+      </c>
+      <c r="D17">
+        <v>3.1804356005440035</v>
+      </c>
+      <c r="E17">
+        <v>42.560620347386958</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18">
+        <v>35.765712346252542</v>
+      </c>
+      <c r="C18">
+        <v>3.9165802098041649</v>
+      </c>
+      <c r="D18">
+        <v>3.2408781032888259</v>
+      </c>
+      <c r="E18">
+        <v>42.923170659345537</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2017</v>
+      </c>
+      <c r="B19">
+        <v>37.532123014477399</v>
+      </c>
+      <c r="C19">
+        <v>3.9508872156038426</v>
+      </c>
+      <c r="D19">
+        <v>3.3091615236876613</v>
+      </c>
+      <c r="E19">
+        <v>44.792171753768905</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2018</v>
+      </c>
+      <c r="B20">
+        <v>35.390410602878596</v>
+      </c>
+      <c r="C20">
+        <v>3.9414837009280421</v>
+      </c>
+      <c r="D20">
+        <v>3.3470800599395005</v>
+      </c>
+      <c r="E20">
+        <v>42.678974363746136</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2019</v>
+      </c>
+      <c r="B21">
+        <v>33.236661131876062</v>
+      </c>
+      <c r="C21">
+        <v>3.9615704811614876</v>
+      </c>
+      <c r="D21">
+        <v>3.4064692453446219</v>
+      </c>
+      <c r="E21">
+        <v>40.604700858382174</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2020</v>
+      </c>
+      <c r="B22">
+        <v>33.314497072240719</v>
+      </c>
+      <c r="C22">
+        <v>3.9151089937202368</v>
+      </c>
+      <c r="D22">
+        <v>3.418709457414463</v>
+      </c>
+      <c r="E22">
+        <v>40.648315523375423</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2021</v>
+      </c>
+      <c r="B23">
+        <v>42.698362997890698</v>
+      </c>
+      <c r="C23">
+        <v>4.018930613573632</v>
+      </c>
+      <c r="D23">
+        <v>3.557060207373143</v>
+      </c>
+      <c r="E23">
+        <v>50.274353818837469</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2022</v>
+      </c>
+      <c r="B24">
+        <v>42.405916804846946</v>
+      </c>
+      <c r="C24">
+        <v>4.0004440074267631</v>
+      </c>
+      <c r="D24">
+        <v>3.6143709279862848</v>
+      </c>
+      <c r="E24">
+        <v>50.020731740259997</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>2023</v>
+      </c>
+      <c r="B25">
+        <v>30.473718717161006</v>
+      </c>
+      <c r="C25">
+        <v>3.9207802958488962</v>
+      </c>
+      <c r="D25">
+        <v>3.592205976150507</v>
+      </c>
+      <c r="E25">
+        <v>37.986704989160415</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>